--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -21398,17 +21398,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1185" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A1185" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1185" s="3" t="s">
-        <v>2646</v>
-      </c>
-      <c r="C1185" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
     <row r="1186" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1186" s="3" t="s">
         <v>12</v>
@@ -21440,17 +21429,6 @@
       </c>
       <c r="C1188" s="1" t="s">
         <v>722</v>
-      </c>
-    </row>
-    <row r="1189" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A1189" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1189" s="3" t="s">
-        <v>2650</v>
-      </c>
-      <c r="C1189" s="1" t="s">
-        <v>2651</v>
       </c>
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.75">

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -8610,8 +8610,10 @@
       <c r="B20" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>45</v>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏سمجهي گيو</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.75">
@@ -8731,8 +8733,10 @@
       <c r="B31" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>70</v>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اْ ارشاد اْپ كوئيي بهي وقت مدد ﴿؟﴾ ني فهرست ما جوئي سكو چھو.</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.75">
@@ -8775,8 +8779,10 @@
       <c r="B35" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>80</v>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏ميقات ما Register تهاوا واسطے مدد، يا اْثثنا تعيين تهئيلا شہر يا zone ما تبديلي ني عرض واسطے مدد.</t>
+        </is>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.75">
@@ -8808,8 +8814,10 @@
       <c r="B38" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>87</v>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏ميقات واسطے Register كرو / اْپ پوتے يا اْثثنا اهل نے Register كرو</t>
+        </is>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.75">
@@ -8896,8 +8904,10 @@
       <c r="B46" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>109</v>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيار ‏الشہر بند تهئي گيو ؛ / اختيار الموضع بند تهئي گيو ؛</t>
+        </is>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.75">
@@ -9226,8 +9236,10 @@
       <c r="B76" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>185</v>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏10 ورس سي ناهنا فرزندو نے اْگل ودھوا پہلا اهنا والدين يا ولي ساتھے جوڑوو لازم چھے.</t>
+        </is>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.75">
@@ -9281,8 +9293,10 @@
       <c r="B81" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>198</v>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏گنجائش پوري تھئي جاسے تو موضع الفصل ني ‏Registration جلدي بند تھئي سكے چھے.</t>
+        </is>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.75">
@@ -9369,8 +9383,10 @@
       <c r="B89" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>217</v>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏Registration 5 June 2026 نے  راتسس 11:59 واجسس بند تھاسے. اْخري تاريخ پہلا گروپ ني سگلي ‏Registration انے رزا ني عرضو پوري كرجو.</t>
+        </is>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.75">
@@ -9380,8 +9396,10 @@
       <c r="B90" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>219</v>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏ريلے مركز: ممبئي</t>
+        </is>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.75">
@@ -9655,8 +9673,10 @@
       <c r="B115" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>281</v>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مؤمن نے  شامل كرو</t>
+        </is>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.75">
@@ -9666,8 +9686,10 @@
       <c r="B116" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>283</v>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏گروپ ما مؤمن نے  شامل كرو</t>
+        </is>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.75">
@@ -9677,8 +9699,10 @@
       <c r="B117" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>286</v>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اْگل ودھوا پہلا اْپ پوتے، اْثثنا اهل نا ممبرو شامل كرو، يا مستحق مهمان نے اذن اْپو.</t>
+        </is>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.75">
@@ -9864,8 +9888,10 @@
       <c r="B134" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>327</v>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏رشته نا عجديدن: ﴿اْپ﴾</t>
+        </is>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.75">
@@ -9875,8 +9901,10 @@
       <c r="B135" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>329</v>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏كيا اهل نا ممبرو حاضر تھاسے يھ چنو. جھ نے ولي يا معاون ني ضرورة چھے يھ نشان تهئيلا چھے — اْگل ودھوا اهنا پہلا مقرر كري نے  جوڑو.</t>
+        </is>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.75">
@@ -10535,8 +10563,10 @@
       <c r="B195" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C195" s="3" t="s">
-        <v>471</v>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نو visa upload كرئيسس</t>
+        </is>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.75">
@@ -10557,8 +10587,10 @@
       <c r="B197" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C197" s="3" t="s">
-        <v>476</v>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏حركة واسطے مدد</t>
+        </is>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.75">
@@ -10568,8 +10600,10 @@
       <c r="B198" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="C198" s="3" t="s">
-        <v>478</v>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏oxygen واسطے مدد</t>
+        </is>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.75">
@@ -10612,8 +10646,10 @@
       <c r="B202" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="C202" s="3" t="s">
-        <v>488</v>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجديد واسطے مدد</t>
+        </is>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.75">
@@ -10634,8 +10670,10 @@
       <c r="B204" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C204" s="3" t="s">
-        <v>493</v>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ديكهوا واسطے مدد</t>
+        </is>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.75">
@@ -10821,8 +10859,10 @@
       <c r="B221" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C221" s="3" t="s">
-        <v>536</v>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نو گروپ جوئي لو. بدلوا واسطے اْپ پاچھا جئي سكو چھو.</t>
+        </is>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.75">
@@ -11184,8 +11224,10 @@
       <c r="B254" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C254" s="3" t="s">
-        <v>617</v>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏مارو reservation هٹاوو</t>
+        </is>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.75">
@@ -11195,8 +11237,10 @@
       <c r="B255" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="C255" s="3" t="s">
-        <v>620</v>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ reservation  كئي طرح بدلوا چاهو چھو يھ چنو.</t>
+        </is>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.75">
@@ -11239,8 +11283,10 @@
       <c r="B259" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="C259" s="3" t="s">
-        <v>631</v>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ سوطط كروا چاهو چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.75">
@@ -11272,8 +11318,10 @@
       <c r="B262" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="C262" s="3" t="s">
-        <v>639</v>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏﴿ممبر﴾ اْثثنا ساتھے reserve تهئيلا چھے. پہلا ﴿ممبر﴾ نے بيجا ولي نے سونپي دو، اهنا بعد اْپ اْثثنو reservation منسوخ كري سكسو.</t>
+        </is>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.75">
@@ -11327,8 +11375,10 @@
       <c r="B267" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="C267" s="3" t="s">
-        <v>651</v>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ ﴿ممبر﴾ نے سونپوا ني عرض موكلي چھے. ﴿ممبر﴾ قبول كرے اهنا بعد ئي اْپ اْثثنو reservation منسوخ كري سكسو.</t>
+        </is>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.75">
@@ -11360,8 +11410,10 @@
       <c r="B270" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="C270" s="3" t="s">
-        <v>659</v>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏reservation هضضي گيو</t>
+        </is>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.75">
@@ -11371,8 +11423,10 @@
       <c r="B271" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="C271" s="3" t="s">
-        <v>661</v>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْثثنو reservation هضضي گيو چھے. اْپ اْ ميقات واسطے دوباره Register تھئي سكو چھو.</t>
+        </is>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.75">
@@ -11404,8 +11458,10 @@
       <c r="B274" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="C274" s="3" t="s">
-        <v>670</v>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اذن موكلائي گيو. يھ اْثثني عرض قبول كرسے اهنا بعد جوواسسس</t>
+        </is>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.75">
@@ -11580,8 +11636,10 @@
       <c r="B290" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="C290" s="3" t="s">
-        <v>712</v>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اْ ممبرو اْثثني ڈابي طرف مقرر  ترتيب نا حساب سي اختيار ‏الشہر ما جاسے. reservation اهيں يھ مرحلا ما تھاسے</t>
+        </is>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.75">
@@ -11668,8 +11726,10 @@
       <c r="B298" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="C298" s="3" t="s">
-        <v>732</v>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اندور ريلے موضع</t>
+        </is>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.75">
@@ -11734,8 +11794,10 @@
       <c r="B304" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="C304" s="3" t="s">
-        <v>748</v>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏مقرر وقت پر سگلا نے ليوا ما اْوسے ، سگلا نے  برابر موقع اْپوا ما اؤسسس</t>
+        </is>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.75">
@@ -11745,8 +11807,10 @@
       <c r="B305" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="C305" s="3" t="s">
-        <v>750</v>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏جلدي اْووا سي پہلا جگہ نتهي ملے.</t>
+        </is>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.75">
@@ -11756,8 +11820,10 @@
       <c r="B306" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="C306" s="3" t="s">
-        <v>752</v>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏نوٹ: اختيار ‏الشہر فقط اهنا واسطے چھے جھ نا پاسے صحيح سفر نا وثائق انے ‏Registration پورو هويھ.</t>
+        </is>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.75">
@@ -12042,8 +12108,10 @@
       <c r="B332" s="3" t="s">
         <v>815</v>
       </c>
-      <c r="C332" s="3" t="s">
-        <v>816</v>
+      <c r="C332" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏﴿شہر﴾ ني تعيين … كھلسے. اهنا وقت اْپ ﴿ممبر﴾ نے reserve كري سكسو.</t>
+        </is>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.75">
@@ -12097,8 +12165,10 @@
       <c r="B337" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="C337" s="3" t="s">
-        <v>829</v>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اهنا بعد هر مستحق ممبر نے اْپ اختيار كريل شہر ما reserve كرو. موجود نتهي نشان والا ممبرو ني تعيين اهيں نه تھئي سكے.</t>
+        </is>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.75">
@@ -12273,8 +12343,10 @@
       <c r="B353" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="C353" s="3" t="s">
-        <v>872</v>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اختيار تهئيلا ريلے موضع﴿شہر﴾ — نيچے سي ممبرو چنو</t>
+        </is>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.75">
@@ -12306,8 +12378,10 @@
       <c r="B356" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="C356" s="3" t="s">
-        <v>878</v>
+      <c r="C356" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ ﴿شہر﴾ ما reserve تهئيلا چھو — اهنے بدلوا چاهو چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.75">
@@ -12529,8 +12603,10 @@
       <c r="B376" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="C376" s="3" t="s">
-        <v>2472</v>
+      <c r="C376" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏form بند تهيو چھے. اْثثنسس جو درست كروو هوئي تو اْثثنا ميقات نا منتظم نے خبر كرو.</t>
+        </is>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.75">
@@ -12617,8 +12693,10 @@
       <c r="B384" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="C384" s="3" t="s">
-        <v>947</v>
+      <c r="C384" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ شوں بدلوا ياهضضاؤا چاهو چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.75">
@@ -12694,8 +12772,10 @@
       <c r="B391" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="C391" s="3" t="s">
-        <v>872</v>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اختيار تهئيلا ريلے موضع﴿شہر﴾ — نيچے سي ممبرو چنو</t>
+        </is>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.75">
@@ -12738,8 +12818,10 @@
       <c r="B395" s="3" t="s">
         <v>972</v>
       </c>
-      <c r="C395" s="3" t="s">
-        <v>973</v>
+      <c r="C395" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ كون نے هضضاؤ چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.75">
@@ -12980,8 +13062,10 @@
       <c r="B417" s="3" t="s">
         <v>1029</v>
       </c>
-      <c r="C417" s="3" t="s">
-        <v>1030</v>
+      <c r="C417" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏﴿شہر﴾ ريلے موضع</t>
+        </is>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.75">
@@ -13145,8 +13229,10 @@
       <c r="B432" s="3" t="s">
         <v>1067</v>
       </c>
-      <c r="C432" s="3" t="s">
-        <v>1068</v>
+      <c r="C432" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ zone A - هال اعظم ما reserve تهئيلا چھو — اهنے بدلوا چاهو چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.75">
@@ -13585,8 +13671,10 @@
       <c r="B472" s="3" t="s">
         <v>1163</v>
       </c>
-      <c r="C472" s="3" t="s">
-        <v>1164</v>
+      <c r="C472" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْثثنو اختيار ‏الشہر  تمام تھيو: ﴿شہر﴾. اْ اْثثنا انے اْثثنا تابع واسطے چھے.</t>
+        </is>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.75">
@@ -13959,8 +14047,10 @@
       <c r="B506" s="3" t="s">
         <v>1242</v>
       </c>
-      <c r="C506" s="3" t="s">
-        <v>1243</v>
+      <c r="C506" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اْ تبديليو منظوري واسطے موكلي دي دھي چھے. جيان لگي جائزو چالو چھے تيان لگي اْپ عرض منسوخ كري سكو چھو.</t>
+        </is>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.75">
@@ -13981,8 +14071,10 @@
       <c r="B508" s="3" t="s">
         <v>1248</v>
       </c>
-      <c r="C508" s="3" t="s">
-        <v>1030</v>
+      <c r="C508" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏﴿شہر﴾ ريلے موضع</t>
+        </is>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.75">
@@ -14003,8 +14095,10 @@
       <c r="B510" s="3" t="s">
         <v>1250</v>
       </c>
-      <c r="C510" s="3" t="s">
-        <v>1030</v>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏﴿شہر﴾ ريلے موضع</t>
+        </is>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.75">
@@ -14102,8 +14196,10 @@
       <c r="B519" s="3" t="s">
         <v>1266</v>
       </c>
-      <c r="C519" s="3" t="s">
-        <v>1267</v>
+      <c r="C519" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏مهمانو نے اهنا ITS ID سي اذن اْپو - يھ قبول كرسے تو اْپ نے جوواسسس.</t>
+        </is>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.75">
@@ -14168,8 +14264,10 @@
       <c r="B525" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="C525" s="3" t="s">
-        <v>1281</v>
+      <c r="C525" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7 احب ريلے مواضع موجود</t>
+        </is>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.75">
@@ -15125,8 +15223,10 @@
       <c r="B612" s="3" t="s">
         <v>1464</v>
       </c>
-      <c r="C612" s="3" t="s">
-        <v>1465</v>
+      <c r="C612" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ پوتے يا اْثثنا اهل نے Register كرو</t>
+        </is>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.75">
@@ -15180,8 +15280,10 @@
       <c r="B617" s="3" t="s">
         <v>1479</v>
       </c>
-      <c r="C617" s="3" t="s">
-        <v>1480</v>
+      <c r="C617" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏سگلا ريلے موضع</t>
+        </is>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.75">
@@ -15620,8 +15722,10 @@
       <c r="B657" s="3" t="s">
         <v>1563</v>
       </c>
-      <c r="C657" s="3" t="s">
-        <v>1480</v>
+      <c r="C657" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏سگلا ريلے موضع</t>
+        </is>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.75">
@@ -15719,8 +15823,10 @@
       <c r="B666" s="3" t="s">
         <v>1583</v>
       </c>
-      <c r="C666" s="3" t="s">
-        <v>1584</v>
+      <c r="C666" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تحقيق كرو كھ اْ اْپ چھو</t>
+        </is>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.75">
@@ -15774,8 +15880,10 @@
       <c r="B671" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="C671" s="3" t="s">
-        <v>1594</v>
+      <c r="C671" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏عرض هضضي گئي</t>
+        </is>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.75">
@@ -15829,8 +15937,10 @@
       <c r="B676" s="3" t="s">
         <v>1604</v>
       </c>
-      <c r="C676" s="3" t="s">
-        <v>1605</v>
+      <c r="C676" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏ميقات هٹاوو</t>
+        </is>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.75">
@@ -15840,8 +15950,10 @@
       <c r="B677" s="3" t="s">
         <v>1606</v>
       </c>
-      <c r="C677" s="3" t="s">
-        <v>1607</v>
+      <c r="C677" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏مارو reservation هٹاوو؟</t>
+        </is>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.75">
@@ -15862,8 +15974,10 @@
       <c r="B679" s="3" t="s">
         <v>1610</v>
       </c>
-      <c r="C679" s="3" t="s">
-        <v>1611</v>
+      <c r="C679" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْثثني اختيار ‏الشہر هٹاوو؟</t>
+        </is>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.75">
@@ -15884,8 +15998,10 @@
       <c r="B681" s="3" t="s">
         <v>1614</v>
       </c>
-      <c r="C681" s="3" t="s">
-        <v>1615</v>
+      <c r="C681" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْثثنو اختيار الموضع هٹاوو؟</t>
+        </is>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.75">
@@ -15917,8 +16033,10 @@
       <c r="B684" s="3" t="s">
         <v>1620</v>
       </c>
-      <c r="C684" s="3" t="s">
-        <v>1621</v>
+      <c r="C684" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيار ‏الشہر هضضي گيو</t>
+        </is>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.75">
@@ -16126,8 +16244,10 @@
       <c r="B703" s="3" t="s">
         <v>1658</v>
       </c>
-      <c r="C703" s="3" t="s">
-        <v>1659</v>
+      <c r="C703" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ شوںهضضاؤا چاهو چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.75">
@@ -16137,8 +16257,10 @@
       <c r="B704" s="3" t="s">
         <v>1660</v>
       </c>
-      <c r="C704" s="3" t="s">
-        <v>1661</v>
+      <c r="C704" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ شوں بدلوا چاهو چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.75">
@@ -16291,8 +16413,10 @@
       <c r="B718" s="3" t="s">
         <v>1688</v>
       </c>
-      <c r="C718" s="3" t="s">
-        <v>1689</v>
+      <c r="C718" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اهوا مواقيت جھ ما اْپ رهي گيل مرحلو فري كھولوا ني عرض كري چھے — منتظم ني منظوري نا انتظار ما.</t>
+        </is>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.75">
@@ -16313,8 +16437,10 @@
       <c r="B720" s="3" t="s">
         <v>1692</v>
       </c>
-      <c r="C720" s="3" t="s">
-        <v>1693</v>
+      <c r="C720" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏عرض تهئي گئي</t>
+        </is>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.75">
@@ -17127,8 +17253,10 @@
       <c r="B794" s="3" t="s">
         <v>1835</v>
       </c>
-      <c r="C794" s="3" t="s">
-        <v>1836</v>
+      <c r="C794" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> چنو كه اْپ حاضر تھاسو كه نتهي.</t>
+        </is>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.75">
@@ -17281,8 +17409,10 @@
       <c r="B808" s="3" t="s">
         <v>1859</v>
       </c>
-      <c r="C808" s="3" t="s">
-        <v>1860</v>
+      <c r="C808" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ اْ ميقات ما حاضر تھاسو؟</t>
+        </is>
       </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.75">
@@ -17534,8 +17664,10 @@
       <c r="B831" s="3" t="s">
         <v>1906</v>
       </c>
-      <c r="C831" s="3" t="s">
-        <v>1907</v>
+      <c r="C831" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏جھ شہرو ما اْپ حاضر تھاوو پسند كرو چھو يھ شامل كرو. شامل كيدا بعد اْپ اهنو ترتيب گوٹھوي سكو چھو — سگلا ما اوپر ني موجود پسندگي پہلا منظور تھاسے.</t>
+        </is>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.75">
@@ -17567,8 +17699,10 @@
       <c r="B834" s="3" t="s">
         <v>1912</v>
       </c>
-      <c r="C834" s="3" t="s">
-        <v>1913</v>
+      <c r="C834" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نكلوا چاهو چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.75">
@@ -17578,8 +17712,10 @@
       <c r="B835" s="3" t="s">
         <v>1914</v>
       </c>
-      <c r="C835" s="3" t="s">
-        <v>1915</v>
+      <c r="C835" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ واقعي اْثثنا ميقات ‏Registration نا account ما سي باهر نكلوا چاهو چھو؟</t>
+        </is>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.75">
@@ -17633,8 +17769,10 @@
       <c r="B840" s="3" t="s">
         <v>1924</v>
       </c>
-      <c r="C840" s="3" t="s">
-        <v>1925</v>
+      <c r="C840" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اْ reservation ما سي اْپ شوںهضضاؤا چاهو چھو يھ اختيار كرو.</t>
+        </is>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.75">
@@ -18084,8 +18222,10 @@
       <c r="B881" s="3" t="s">
         <v>2004</v>
       </c>
-      <c r="C881" s="3" t="s">
-        <v>2005</v>
+      <c r="C881" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏اْ ‏Registration ني عرض منتظم ني منظوري نا انتظار ما چھے — اْ يھ ممبرو چھے جھ ني اْپ عرض كري چھے.</t>
+        </is>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.75">
@@ -18271,8 +18411,10 @@
       <c r="B898" s="3" t="s">
         <v>2036</v>
       </c>
-      <c r="C898" s="3" t="s">
-        <v>2037</v>
+      <c r="C898" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْثثني جماعة نو وقت پورو تمام چھے. اْپ Round 2 ما فري reserve كري سكو چھو، جھ سگلا واسطے كھولو چھے.</t>
+        </is>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.75">
@@ -18282,8 +18424,10 @@
       <c r="B899" s="3" t="s">
         <v>2038</v>
       </c>
-      <c r="C899" s="3" t="s">
-        <v>2039</v>
+      <c r="C899" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">‏عرض منظور تھايھ تيان لگي اْثثنو هال نو reservation اهم نو اهم رهسے. اْپ اهني حالت reservation ما تبديلي كرو نا صفحا پر جوئي سكو چھو يا منسوخ كري سكو چھو.</t>
+        </is>
       </c>
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.75">
@@ -20108,8 +20252,10 @@
       <c r="B1065" s="3" t="s">
         <v>2339</v>
       </c>
-      <c r="C1065" s="3" t="s">
-        <v>2340</v>
+      <c r="C1065" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مظظمان نے اذن اْپو ، يھ قبول كرسے تو ساتهسس جوواسسس</t>
+        </is>
       </c>
     </row>
     <row r="1066" spans="1:3" x14ac:dyDescent="0.75">
@@ -20130,8 +20276,10 @@
       <c r="B1067" s="3" t="s">
         <v>2343</v>
       </c>
-      <c r="C1067" s="3" t="s">
-        <v>2344</v>
+      <c r="C1067" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">list ما سي چنو</t>
+        </is>
       </c>
     </row>
     <row r="1068" spans="1:3" x14ac:dyDescent="0.75">
@@ -20163,8 +20311,10 @@
       <c r="B1070" s="3" t="s">
         <v>2351</v>
       </c>
-      <c r="C1070" s="3" t="s">
-        <v>2352</v>
+      <c r="C1070" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إدارة الميقات نا خدمةككزار يھ اْپ نے عيد غديرخم واسطے Register كيدا ؛</t>
+        </is>
       </c>
     </row>
     <row r="1071" spans="1:3" x14ac:dyDescent="0.75">
@@ -20218,8 +20368,10 @@
       <c r="B1075" s="3" t="s">
         <v>2363</v>
       </c>
-      <c r="C1075" s="3" t="s">
-        <v>2364</v>
+      <c r="C1075" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فصل! مؤمنين نے العشرة المباركة 1448ھ واسطے رزا طلب كروا نو اذن ؛ ، خدا تع سگلا نے ياري انے توفيق اْثثسس</t>
+        </is>
       </c>
     </row>
     <row r="1076" spans="1:3" x14ac:dyDescent="0.75">
@@ -20229,8 +20381,10 @@
       <c r="B1076" s="3" t="s">
         <v>2366</v>
       </c>
-      <c r="C1076" s="3" t="s">
-        <v>2367</v>
+      <c r="C1076" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ولي + تابع + Registered سگلا ساتهسس</t>
+        </is>
       </c>
     </row>
     <row r="1077" spans="1:3" x14ac:dyDescent="0.75">
@@ -20262,8 +20416,10 @@
       <c r="B1079" s="3" t="s">
         <v>2372</v>
       </c>
-      <c r="C1079" s="3" t="s">
-        <v>2373</v>
+      <c r="C1079" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نو شهر كولمبو confirm تهيو ؛، اْ اْپ انے اْثثنا تابع سگلا نا واسطے ؛</t>
+        </is>
       </c>
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.75">
@@ -20273,8 +20429,10 @@
       <c r="B1080" s="3" t="s">
         <v>2374</v>
       </c>
-      <c r="C1080" s="3" t="s">
-        <v>2375</v>
+      <c r="C1080" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نے عيد غديرخم واسطے رزا فضل تهئي ؛ ، يظظاطط اْپ ني رزا ديكهي download كري سكائسس ؛</t>
+        </is>
       </c>
     </row>
     <row r="1081" spans="1:3" x14ac:dyDescent="0.75">
@@ -20335,8 +20493,10 @@
       <c r="B1087" s="3" t="s">
         <v>2473</v>
       </c>
-      <c r="C1087" s="1" t="s">
-        <v>2474</v>
+      <c r="C1087" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ممبر چنو</t>
+        </is>
       </c>
     </row>
     <row r="1088" spans="1:3" x14ac:dyDescent="0.75">
@@ -20355,8 +20515,10 @@
       <c r="B1089" s="3" t="s">
         <v>2476</v>
       </c>
-      <c r="C1089" s="2" t="s">
-        <v>2477</v>
+      <c r="C1089" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11:59 اختيار الشہر كهلوا پہلا</t>
+        </is>
       </c>
     </row>
     <row r="1090" spans="1:3" x14ac:dyDescent="0.75">
@@ -20419,8 +20581,10 @@
       <c r="B1095" s="3" t="s">
         <v>2485</v>
       </c>
-      <c r="C1095" s="1" t="s">
-        <v>2486</v>
+      <c r="C1095" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نا طرف سي خدمة ككزار register تهئي گيا ؛</t>
+        </is>
       </c>
     </row>
     <row r="1096" spans="1:3" x14ac:dyDescent="0.75">
@@ -20452,8 +20616,10 @@
       <c r="B1098" s="3" t="s">
         <v>2491</v>
       </c>
-      <c r="C1098" s="1" t="s">
-        <v>2492</v>
+      <c r="C1098" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سگلا</t>
+        </is>
       </c>
     </row>
     <row r="1099" spans="1:3" x14ac:dyDescent="0.75">
@@ -20485,8 +20651,10 @@
       <c r="B1101" s="3" t="s">
         <v>2495</v>
       </c>
-      <c r="C1101" s="1" t="s">
-        <v>2496</v>
+      <c r="C1101" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نے إدارة الميقات نا خدمة ككزار  يھ عيد غديرخم واسطے register كيدا ؛</t>
+        </is>
       </c>
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.75">
@@ -20496,8 +20664,10 @@
       <c r="B1102" s="3" t="s">
         <v>2497</v>
       </c>
-      <c r="C1102" s="1" t="s">
-        <v>2498</v>
+      <c r="C1102" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عرض - احب شہر</t>
+        </is>
       </c>
     </row>
     <row r="1103" spans="1:3" x14ac:dyDescent="0.75">
@@ -20540,8 +20710,10 @@
       <c r="B1106" s="3" t="s">
         <v>2505</v>
       </c>
-      <c r="C1106" s="1" t="s">
-        <v>2506</v>
+      <c r="C1106" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ريلے موضع بدلو</t>
+        </is>
       </c>
     </row>
     <row r="1107" spans="1:3" x14ac:dyDescent="0.75">
@@ -20562,8 +20734,10 @@
       <c r="B1108" s="3" t="s">
         <v>2509</v>
       </c>
-      <c r="C1108" s="1" t="s">
-        <v>2510</v>
+      <c r="C1108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شہر چنو</t>
+        </is>
       </c>
     </row>
     <row r="1109" spans="1:3" x14ac:dyDescent="0.75">
@@ -20595,8 +20769,10 @@
       <c r="B1111" s="3" t="s">
         <v>2513</v>
       </c>
-      <c r="C1111" s="1" t="s">
-        <v>2514</v>
+      <c r="C1111" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">موضع الفصل ما تعيين واسطے ممبرو چنو</t>
+        </is>
       </c>
     </row>
     <row r="1112" spans="1:3" x14ac:dyDescent="0.75">
@@ -20615,8 +20791,10 @@
       <c r="B1113" s="3" t="s">
         <v>2516</v>
       </c>
-      <c r="C1113" s="1" t="s">
-        <v>2517</v>
+      <c r="C1113" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شہر</t>
+        </is>
       </c>
     </row>
     <row r="1114" spans="1:3" x14ac:dyDescent="0.75">
@@ -20626,8 +20804,10 @@
       <c r="B1114" s="3" t="s">
         <v>2518</v>
       </c>
-      <c r="C1114" s="1" t="s">
-        <v>2519</v>
+      <c r="C1114" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شہر ني ترتيب</t>
+        </is>
       </c>
     </row>
     <row r="1115" spans="1:3" x14ac:dyDescent="0.75">
@@ -20637,8 +20817,10 @@
       <c r="B1115" s="3" t="s">
         <v>2520</v>
       </c>
-      <c r="C1115" s="1" t="s">
-        <v>2521</v>
+      <c r="C1115" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيار الشہر بيد تهئي گيو ؛</t>
+        </is>
       </c>
     </row>
     <row r="1116" spans="1:3" x14ac:dyDescent="0.75">
@@ -20846,8 +21028,10 @@
       <c r="B1134" s="3" t="s">
         <v>2553</v>
       </c>
-      <c r="C1134" s="1" t="s">
-        <v>2554</v>
+      <c r="C1134" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْ سگلا مظظمانو</t>
+        </is>
       </c>
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.75">
@@ -20901,8 +21085,10 @@
       <c r="B1139" s="3" t="s">
         <v>2563</v>
       </c>
-      <c r="C1139" s="1" t="s">
-        <v>2564</v>
+      <c r="C1139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مرتضى بهائي معز بهائي ككهي ولا نے اْپ يھ محافظ ححنا ؛ ، عرض قبول كريئسس </t>
+        </is>
       </c>
     </row>
     <row r="1140" spans="1:3" x14ac:dyDescent="0.75">
@@ -20912,8 +21098,10 @@
       <c r="B1140" s="3" t="s">
         <v>2565</v>
       </c>
-      <c r="C1140" s="1" t="s">
-        <v>2566</v>
+      <c r="C1140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مرتضى بهائي معز بهائي ككهي ولا يھ اْپ نے اهنا گروپ ما اذن اْپو ؛</t>
+        </is>
       </c>
     </row>
     <row r="1141" spans="1:3" x14ac:dyDescent="0.75">
@@ -20967,8 +21155,10 @@
       <c r="B1145" s="3" t="s">
         <v>2575</v>
       </c>
-      <c r="C1145" s="1" t="s">
-        <v>2576</v>
+      <c r="C1145" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بيجا شہر</t>
+        </is>
       </c>
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.75">
@@ -21000,8 +21190,10 @@
       <c r="B1148" s="3" t="s">
         <v>2580</v>
       </c>
-      <c r="C1148" s="1" t="s">
-        <v>2581</v>
+      <c r="C1148" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نا reservation نا ممبرو</t>
+        </is>
       </c>
     </row>
     <row r="1149" spans="1:3" x14ac:dyDescent="0.75">
@@ -21011,8 +21203,10 @@
       <c r="B1149" s="3" t="s">
         <v>2582</v>
       </c>
-      <c r="C1149" s="1" t="s">
-        <v>2583</v>
+      <c r="C1149" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">هجي اْپ نا گروپ نے رزا نتهي ملي</t>
+        </is>
       </c>
     </row>
     <row r="1150" spans="1:3" x14ac:dyDescent="0.75">
@@ -21055,8 +21249,10 @@
       <c r="B1153" s="3" t="s">
         <v>2590</v>
       </c>
-      <c r="C1153" s="1" t="s">
-        <v>2591</v>
+      <c r="C1153" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اغلاط درست كراوا واسطے اْپ نا ميقات نا coordinator نے خبر كريئسس </t>
+        </is>
       </c>
     </row>
     <row r="1154" spans="1:3" x14ac:dyDescent="0.75">
@@ -21066,8 +21262,10 @@
       <c r="B1154" s="3" t="s">
         <v>2592</v>
       </c>
-      <c r="C1154" s="1" t="s">
-        <v>2593</v>
+      <c r="C1154" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">registration واسطے تيار</t>
+        </is>
       </c>
     </row>
     <row r="1155" spans="1:3" x14ac:dyDescent="0.75">
@@ -21097,8 +21295,10 @@
       <c r="B1157" s="3" t="s">
         <v>2597</v>
       </c>
-      <c r="C1157" s="1" t="s">
-        <v>2598</v>
+      <c r="C1157" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ريلے</t>
+        </is>
       </c>
     </row>
     <row r="1158" spans="1:3" x14ac:dyDescent="0.75">
@@ -21130,8 +21330,10 @@
       <c r="B1160" s="3" t="s">
         <v>2603</v>
       </c>
-      <c r="C1160" s="1" t="s">
-        <v>2604</v>
+      <c r="C1160" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سگلا واسطے عرض</t>
+        </is>
       </c>
     </row>
     <row r="1161" spans="1:3" x14ac:dyDescent="0.75">
@@ -21141,8 +21343,10 @@
       <c r="B1161" s="3" t="s">
         <v>2605</v>
       </c>
-      <c r="C1161" s="1" t="s">
-        <v>2606</v>
+      <c r="C1161" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عرض تهئي گئي</t>
+        </is>
       </c>
     </row>
     <row r="1162" spans="1:3" x14ac:dyDescent="0.75">
@@ -21240,8 +21444,10 @@
       <c r="B1170" s="3" t="s">
         <v>2623</v>
       </c>
-      <c r="C1170" s="1" t="s">
-        <v>2624</v>
+      <c r="C1170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جككه واسطے تذكار</t>
+        </is>
       </c>
     </row>
     <row r="1171" spans="1:3" x14ac:dyDescent="0.75">
@@ -21273,8 +21479,10 @@
       <c r="B1173" s="3" t="s">
         <v>2627</v>
       </c>
-      <c r="C1173" s="1" t="s">
-        <v>2628</v>
+      <c r="C1173" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قبول تهاوا واسطے موكليسس</t>
+        </is>
       </c>
     </row>
     <row r="1174" spans="1:3" x14ac:dyDescent="0.75">
@@ -21328,8 +21536,10 @@
       <c r="B1178" s="3" t="s">
         <v>2635</v>
       </c>
-      <c r="C1178" s="1" t="s">
-        <v>2636</v>
+      <c r="C1178" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شروط انے احكام</t>
+        </is>
       </c>
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.75">
@@ -21339,8 +21549,10 @@
       <c r="B1179" s="3" t="s">
         <v>2637</v>
       </c>
-      <c r="C1179" s="1" t="s">
-        <v>2638</v>
+      <c r="C1179" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ ني ميقات ني تمام سفر يظظاطط ديكهيئسس </t>
+        </is>
       </c>
     </row>
     <row r="1180" spans="1:3" x14ac:dyDescent="0.75">
@@ -21350,8 +21562,10 @@
       <c r="B1180" s="3" t="s">
         <v>2639</v>
       </c>
-      <c r="C1180" s="1" t="s">
-        <v>2640</v>
+      <c r="C1180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْ ميقات واسطے هوے register نظظيطط تهئي سكائسس</t>
+        </is>
       </c>
     </row>
     <row r="1181" spans="1:3" x14ac:dyDescent="0.75">
@@ -21438,8 +21652,10 @@
       <c r="B1190" s="3" t="s">
         <v>2652</v>
       </c>
-      <c r="C1190" s="1" t="s">
-        <v>2653</v>
+      <c r="C1190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيار الشہر نو ثثظظلو phase جلدي كلاك ما كهلسسس</t>
+        </is>
       </c>
     </row>
     <row r="1191" spans="1:3" x14ac:dyDescent="0.75">
@@ -21449,8 +21665,10 @@
       <c r="B1191" s="3" t="s">
         <v>2654</v>
       </c>
-      <c r="C1191" s="1" t="s">
-        <v>2655</v>
+      <c r="C1191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اْپ نا register كيديلا مواقيت</t>
+        </is>
       </c>
     </row>
     <row r="1192" spans="1:3" x14ac:dyDescent="0.75">
@@ -21460,8 +21678,10 @@
       <c r="B1192" s="3" t="s">
         <v>2656</v>
       </c>
-      <c r="C1192" s="1" t="s">
-        <v>2657</v>
+      <c r="C1192" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيار الموضع بند تهئي گيو ؛</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -13079,8 +13079,10 @@
       <c r="B426" s="3" t="s">
         <v>1054</v>
       </c>
-      <c r="C426" s="3" t="s">
-        <v>1055</v>
+      <c r="C426" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 ممبرو نو zone ما هجي تعيين تھيو نتهي. اهنا بغير اْگل ودھوو؟</t>
+        </is>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.75">

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -10656,8 +10656,10 @@
       <c r="B206" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C206" s="3" t="s">
-        <v>499</v>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بيجو نمبر، اگر هوئسس تو</t>
+        </is>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.75">

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -8689,8 +8689,10 @@
       <c r="B27" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>61</v>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registration شروع تهاوا ما</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.75">
@@ -11149,8 +11151,10 @@
       <c r="B247" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="C247" s="3" t="s">
-        <v>598</v>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختيار الشہر بند تهئي گيو ؛</t>
+        </is>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.75">
@@ -11160,8 +11164,10 @@
       <c r="B248" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="C248" s="3" t="s">
-        <v>601</v>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">زون اختيار كرو</t>
+        </is>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.75">
@@ -13053,8 +13059,10 @@
       <c r="B416" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="C416" s="3" t="s">
-        <v>1027</v>
+      <c r="C416" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">شہر انے زون</t>
+        </is>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.75">
@@ -16430,8 +16438,10 @@
       <c r="B719" s="3" t="s">
         <v>1690</v>
       </c>
-      <c r="C719" s="3" t="s">
-        <v>1691</v>
+      <c r="C719" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registration بند تھئي گيو چھے.</t>
+        </is>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.75">

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -8634,8 +8634,10 @@
       <c r="B22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>51</v>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مواقيت Registered</t>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.75">
@@ -9117,8 +9119,10 @@
       <c r="B65" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>156</v>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سگلا مواقيت</t>
+        </is>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.75">
@@ -9139,8 +9143,10 @@
       <c r="B67" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>161</v>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تمام مواقيت يہاں ديكهي سكائے ؛.</t>
+        </is>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.75">

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -8396,7 +8396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1192"/>
+  <dimension ref="A1:F1193"/>
   <sheetFormatPr defaultRowHeight="22.2" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="3" customWidth="1"/>
@@ -21701,6 +21701,18 @@
       <c r="C1192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">اختيار الموضع بند تهئي گيو ؛</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193" spans="1:3">
+      <c r="B1193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone closes in {date}</t>
+        </is>
+      </c>
+      <c r="C1193" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thu, 25 Jun 2026 · 11:59 PM IST نے زون بند تهاسے</t>
         </is>
       </c>
     </row>

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -17734,7 +17734,7 @@
       </c>
       <c r="C835" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">اْپ واقعي اْثثنا ميقات ‏Registration نا account ما سي باهر نكلوا چاهو چھو؟</t>
+          <t xml:space="preserve">اْپ ميقات سي باهر نكلوا چاهو چھو؟</t>
         </is>
       </c>
     </row>

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -8511,8 +8511,10 @@
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>19</v>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">داخل تھاوا واسطے اْپ نا ITS نا تفاصيل نو استعمال كرو</t>
+        </is>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.75">

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -9191,8 +9191,10 @@
       <c r="B71" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>61</v>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registration كھلوا ما</t>
+        </is>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.75">

--- a/RMS_Mumineen_LSD_wordlist_v4.xlsx
+++ b/RMS_Mumineen_LSD_wordlist_v4.xlsx
@@ -8513,7 +8513,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">داخل تھاوا واسطے اْپ نا ITS نا تفاصيل نو استعمال كرو</t>
+          <t xml:space="preserve">اْپ نا ITS نا تفاصيل درج كريئے</t>
         </is>
       </c>
     </row>
@@ -8649,8 +8649,10 @@
       <c r="B23" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registration تمام</t>
+        </is>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.75">
@@ -8660,8 +8662,10 @@
       <c r="B24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>55</v>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registration تمام تهاوا ما</t>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.75">
@@ -9193,7 +9197,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registration كھلوا ما</t>
+          <t xml:space="preserve">Registration شروع تهاوا ما</t>
         </is>
       </c>
     </row>
@@ -14948,8 +14952,10 @@
       <c r="B585" s="3" t="s">
         <v>1411</v>
       </c>
-      <c r="C585" s="3" t="s">
-        <v>1191</v>
+      <c r="C585" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اخرج</t>
+        </is>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.75">
@@ -15667,8 +15673,10 @@
       <c r="B650" s="3" t="s">
         <v>1546</v>
       </c>
-      <c r="C650" s="3" t="s">
-        <v>1547</v>
+      <c r="C650" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registration شروع كرو</t>
+        </is>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.75">
@@ -16450,7 +16458,7 @@
       </c>
       <c r="C719" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Registration بند تھئي گيو چھے.</t>
+          <t xml:space="preserve">Registration تمام تھئي گيو چھے.</t>
         </is>
       </c>
     </row>
@@ -17644,8 +17652,10 @@
       <c r="B827" s="3" t="s">
         <v>1899</v>
       </c>
-      <c r="C827" s="3" t="s">
-        <v>1900</v>
+      <c r="C827" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS ID برابر 8 عدد نو هوو جوئيے</t>
+        </is>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.75">
